--- a/Assets/SheetXExample/Examples/Exporting Multiple Excel Files/GameData.xlsx
+++ b/Assets/SheetXExample/Examples/Exporting Multiple Excel Files/GameData.xlsx
@@ -4089,17 +4089,17 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="134"/>
